--- a/ci-cd-merge-resolver/repoCollector/datasets/zemberek-nlp.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/zemberek-nlp.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,31 +44,22 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>7711e2b3aa4c8af84843697c4fba43e20928f812</t>
-  </si>
-  <si>
-    <t>91575570d8711861f5922cfa278151b208b23aca</t>
-  </si>
-  <si>
-    <t>edbcc0ed671450bbe852c22964b56ae936f108c4</t>
-  </si>
-  <si>
-    <t>a08151ed6c860420aa9324188d3614357d10bd70</t>
-  </si>
-  <si>
-    <t>0540e4c08e0587ac91f252773f3bf1cf9652896c</t>
-  </si>
-  <si>
-    <t>94475885daec813e585283d1b7722690ed3d4848</t>
-  </si>
-  <si>
-    <t>8a31894dcccdaa358d3784e2380d92c1c01fa8a5</t>
-  </si>
-  <si>
-    <t>e47b3c342437f636a0b189f3c2d2fd23104a6760</t>
-  </si>
-  <si>
-    <t>3ea7cbfc472153e4273e9581bb4b0579512cbc01</t>
+    <t>0bcfe040d8606f0a0cea5d5fa5c862274da3ae19</t>
+  </si>
+  <si>
+    <t>025b9f1e73a61a46549b7cab70e4e77e714169b5</t>
+  </si>
+  <si>
+    <t>a8543368b3c37ce57ac2fa8726528ab7d4bc436f</t>
+  </si>
+  <si>
+    <t>fe6d0f81ba56234527fc2d611e405ca588a8575e</t>
+  </si>
+  <si>
+    <t>5b63a2905ab6ba8697c4f01085a8ebf67ce5653f</t>
+  </si>
+  <si>
+    <t>c79cb3f655d0e4363736d71bd78c0f037ff0340f</t>
   </si>
   <si>
     <t>cba3cefdbf185e9a4c21dc668f9600023b260146</t>
@@ -80,6 +71,15 @@
     <t>d7b46d9a18b636811d15b7fedefce8318e718342</t>
   </si>
   <si>
+    <t>35c0a29aff284803da960baf773631d270c26997</t>
+  </si>
+  <si>
+    <t>1956f3a23dcf664b5dfb948a85e3b839ea020131</t>
+  </si>
+  <si>
+    <t>068524ee396bcdfd2dce05ccc3d757b1e50e5444</t>
+  </si>
+  <si>
     <t>e497b43183da07131fc2fa7bd4f05b578b3d70a9</t>
   </si>
   <si>
@@ -87,24 +87,6 @@
   </si>
   <si>
     <t>9ec48c53d9faf2a537129f2f28ef0587d4a1ef1e</t>
-  </si>
-  <si>
-    <t>35c0a29aff284803da960baf773631d270c26997</t>
-  </si>
-  <si>
-    <t>1956f3a23dcf664b5dfb948a85e3b839ea020131</t>
-  </si>
-  <si>
-    <t>068524ee396bcdfd2dce05ccc3d757b1e50e5444</t>
-  </si>
-  <si>
-    <t>0bcfe040d8606f0a0cea5d5fa5c862274da3ae19</t>
-  </si>
-  <si>
-    <t>025b9f1e73a61a46549b7cab70e4e77e714169b5</t>
-  </si>
-  <si>
-    <t>a8543368b3c37ce57ac2fa8726528ab7d4bc436f</t>
   </si>
   <si>
     <t>4b39a3ee35ffcf61f66a783dde2af1d9fbd9c12a</t>
@@ -158,7 +140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -204,13 +186,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>39.0</v>
+        <v>252.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -219,10 +201,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.5699999928474426</v>
+        <v>4.776000022888184</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -236,7 +218,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>40.0</v>
+        <v>126.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -251,10 +233,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.6200000047683716</v>
+        <v>17.573997497558594</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -268,7 +250,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>40.0</v>
+        <v>71.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -283,10 +265,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.5839999914169312</v>
+        <v>3.2189998626708984</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -300,25 +282,25 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>72.0</v>
+        <v>244.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>3.2180004119873047</v>
+        <v>3.821000099182129</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -332,7 +314,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>272.0</v>
+        <v>236.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>3.0</v>
@@ -347,10 +329,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>10.08699893951416</v>
+        <v>3.580000162124634</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -364,13 +346,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>282.0</v>
+        <v>266.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -379,74 +361,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>10.86199951171875</v>
+        <v>10.142998695373535</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="D8" t="n" s="0">
-        <v>556.0</v>
-      </c>
-      <c r="E8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G8" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n" s="0">
-        <v>14.22800350189209</v>
-      </c>
-      <c r="J8" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D9" t="n" s="0">
-        <v>575.0</v>
-      </c>
-      <c r="E9" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F9" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G9" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n" s="0">
-        <v>18.4220027923584</v>
-      </c>
-      <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
